--- a/data/trans_orig/P1407-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2012</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,74 +1089,74 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8620</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>9373</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3767</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9406</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3767</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>9489</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,77 +1202,77 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>606488</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>601635</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>609234</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1293575</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1287969</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1296421</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>606488</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>600849</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>609328</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1293575</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1287853</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1296396</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>679855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>681863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693766</t>
+          <t>693474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705796</t>
+          <t>705833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1375455</t>
+          <t>1374088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387776</t>
+          <t>1387689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21026</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>11254</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>5330</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20808</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>11254</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>5385</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612468</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>614617</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593456</t>
+          <t>593238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608934</t>
+          <t>609085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1208676</t>
+          <t>1208822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223495</t>
+          <t>1223550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27995</t>
+          <t>28460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>28125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>429429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419805</t>
+          <t>419340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>437250</t>
+          <t>437596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848197</t>
+          <t>849104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866854</t>
+          <t>866908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297823</t>
+          <t>297919</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307743</t>
+          <t>307741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335342</t>
+          <t>336322</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348233</t>
+          <t>348417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637132</t>
+          <t>638624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>653291</t>
+          <t>653982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>30157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36088</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238911</t>
+          <t>238729</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248793</t>
+          <t>248792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>357532</t>
+          <t>357639</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>374875</t>
+          <t>375838</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>601559</t>
+          <t>602055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>621544</t>
+          <t>621782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>89920</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101985</t>
+          <t>101316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3407307</t>
+          <t>3408524</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3421621</t>
+          <t>3421699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3465342</t>
+          <t>3463996</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3499265</t>
+          <t>3498798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6878709</t>
+          <t>6879378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6915643</t>
+          <t>6915546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2016</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,97 +3710,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4963</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>996</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5621</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6011</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390134</t>
+          <t>390792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810228</t>
+          <t>809207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556187</t>
+          <t>556263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1146504</t>
+          <t>1146644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153160</t>
+          <t>1153156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651542</t>
+          <t>651788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660409</t>
+          <t>660407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1320909</t>
+          <t>1319667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329504</t>
+          <t>1329497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640713</t>
+          <t>640385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637452</t>
+          <t>637407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647140</t>
+          <t>647105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1282029</t>
+          <t>1281578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1292884</t>
+          <t>1292892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>22261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472485</t>
+          <t>472143</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474846</t>
+          <t>474588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490607</t>
+          <t>490814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>949400</t>
+          <t>951009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>967459</t>
+          <t>967447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>32788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318410</t>
+          <t>317894</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330509</t>
+          <t>330227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>356643</t>
+          <t>356006</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370903</t>
+          <t>370941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>678528</t>
+          <t>679304</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>698373</t>
+          <t>698610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>34015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39593</t>
+          <t>39816</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245465</t>
+          <t>245247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254520</t>
+          <t>254528</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365561</t>
+          <t>366154</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386756</t>
+          <t>387486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>617574</t>
+          <t>617351</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>639578</t>
+          <t>639359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>76735</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59773</t>
+          <t>58722</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96054</t>
+          <t>95206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3367378</t>
+          <t>3368750</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3384619</t>
+          <t>3384734</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3467533</t>
+          <t>3467807</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3499749</t>
+          <t>3500917</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6842838</t>
+          <t>6843686</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6879119</t>
+          <t>6880170</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1407-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Edad-trans_orig.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>601635</t>
+          <t>600790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609234</t>
+          <t>609302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287969</t>
+          <t>1288467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296421</t>
+          <t>1296403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>693474</t>
+          <t>693367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705833</t>
+          <t>706590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1374088</t>
+          <t>1376630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387689</t>
+          <t>1388484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593238</t>
+          <t>593390</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>609085</t>
+          <t>608812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1208822</t>
+          <t>1208073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223550</t>
+          <t>1223471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28125</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419340</t>
+          <t>420797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>437596</t>
+          <t>437604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>849104</t>
+          <t>848981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866908</t>
+          <t>866738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297919</t>
+          <t>297327</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307741</t>
+          <t>306798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336322</t>
+          <t>335300</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348417</t>
+          <t>348200</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>638624</t>
+          <t>638509</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>653982</t>
+          <t>654229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30157</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>36901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238729</t>
+          <t>239737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248792</t>
+          <t>248852</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>357639</t>
+          <t>356138</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375838</t>
+          <t>374652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>602055</t>
+          <t>600746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>621782</t>
+          <t>621401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89920</t>
+          <t>94767</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65148</t>
+          <t>64896</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101316</t>
+          <t>102906</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3408524</t>
+          <t>3407684</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3421699</t>
+          <t>3421619</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3463996</t>
+          <t>3459149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3498798</t>
+          <t>3497911</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6879378</t>
+          <t>6877788</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6915546</t>
+          <t>6915798</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390792</t>
+          <t>389708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809207</t>
+          <t>809831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556263</t>
+          <t>556250</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562662</t>
+          <t>562673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1146644</t>
+          <t>1146803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153156</t>
+          <t>1153161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651788</t>
+          <t>651051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660407</t>
+          <t>660405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1319667</t>
+          <t>1320024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329497</t>
+          <t>1329503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640385</t>
+          <t>641110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637407</t>
+          <t>636977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647105</t>
+          <t>647138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1281578</t>
+          <t>1282624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1292892</t>
+          <t>1293037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22261</t>
+          <t>21964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472143</t>
+          <t>472790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474588</t>
+          <t>474885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490814</t>
+          <t>490741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>951009</t>
+          <t>950325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>967447</t>
+          <t>967435</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>16820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32788</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>317894</t>
+          <t>317510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330227</t>
+          <t>330320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>356006</t>
+          <t>356072</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370941</t>
+          <t>370945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>679304</t>
+          <t>678876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>698610</t>
+          <t>699048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34015</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>17300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39816</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245247</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254528</t>
+          <t>254547</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>366154</t>
+          <t>366097</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387486</t>
+          <t>386515</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>617351</t>
+          <t>618142</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>639359</t>
+          <t>639867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43625</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76735</t>
+          <t>78059</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58722</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95206</t>
+          <t>95174</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3368750</t>
+          <t>3368719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3384734</t>
+          <t>3384633</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3467807</t>
+          <t>3466483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3500917</t>
+          <t>3499032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6843686</t>
+          <t>6843718</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6880170</t>
+          <t>6880841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
